--- a/shipping/sample/momo訂單匯出範例.xlsx
+++ b/shipping/sample/momo訂單匯出範例.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="105">
   <si>
     <t>訂單編號</t>
   </si>
@@ -59,6 +59,15 @@
   </si>
   <si>
     <t>數量</t>
+  </si>
+  <si>
+    <t>售價(含稅)</t>
+  </si>
+  <si>
+    <t>進價(含稅)</t>
+  </si>
+  <si>
+    <t>發票日期</t>
   </si>
   <si>
     <t>代收款</t>
@@ -697,17 +706,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="9" width="16" customWidth="1"/>
     <col min="10" max="10" width="34" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="60" customWidth="1"/>
-    <col min="13" max="19" width="16" customWidth="1"/>
+    <col min="13" max="22" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -765,229 +774,265 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="O2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P2">
         <v>1</v>
       </c>
       <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>599</v>
+      </c>
+      <c r="R2">
+        <v>520</v>
+      </c>
+      <c r="S2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" t="s">
         <v>34</v>
       </c>
-      <c r="S2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" t="s">
-        <v>44</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
-      </c>
       <c r="N3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P3">
         <v>1</v>
       </c>
       <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>1580</v>
+      </c>
+      <c r="R3">
+        <v>1100</v>
+      </c>
+      <c r="S3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3" t="s">
+        <v>49</v>
+      </c>
+      <c r="V3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" t="s">
         <v>46</v>
       </c>
-      <c r="S3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K4" t="s">
-        <v>43</v>
-      </c>
       <c r="L4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P4">
         <v>1</v>
       </c>
       <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4" t="s">
-        <v>46</v>
+        <v>1580</v>
+      </c>
+      <c r="R4">
+        <v>1100</v>
       </c>
       <c r="S4" t="s">
-        <v>33</v>
+        <v>39</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4" t="s">
+        <v>49</v>
+      </c>
+      <c r="V4" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P5">
         <v>2</v>
@@ -995,117 +1040,135 @@
       <c r="Q5">
         <v>0</v>
       </c>
-      <c r="R5" t="s">
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5" t="s">
+        <v>39</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5" t="s">
+        <v>49</v>
+      </c>
+      <c r="V5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" t="s">
+        <v>60</v>
+      </c>
+      <c r="J6" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" t="s">
         <v>46</v>
       </c>
-      <c r="S5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I6" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" t="s">
-        <v>43</v>
-      </c>
       <c r="L6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P6">
         <v>1</v>
       </c>
       <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>1580</v>
+      </c>
+      <c r="R6">
+        <v>1100</v>
+      </c>
+      <c r="S6" t="s">
+        <v>23</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6" t="s">
+        <v>62</v>
+      </c>
+      <c r="V6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
         <v>59</v>
       </c>
-      <c r="S6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="I7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J7" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7" t="s">
         <v>53</v>
       </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="M7" t="s">
+        <v>34</v>
+      </c>
+      <c r="N7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O7" t="s">
         <v>54</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J7" t="s">
-        <v>58</v>
-      </c>
-      <c r="K7" t="s">
-        <v>49</v>
-      </c>
-      <c r="L7" t="s">
-        <v>50</v>
-      </c>
-      <c r="M7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" t="s">
-        <v>33</v>
-      </c>
-      <c r="O7" t="s">
-        <v>51</v>
       </c>
       <c r="P7">
         <v>1</v>
@@ -1113,117 +1176,135 @@
       <c r="Q7">
         <v>0</v>
       </c>
-      <c r="R7" t="s">
-        <v>59</v>
+      <c r="R7">
+        <v>0</v>
       </c>
       <c r="S7" t="s">
-        <v>33</v>
+        <v>23</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" t="s">
+        <v>62</v>
+      </c>
+      <c r="V7" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="O8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P8">
         <v>1</v>
       </c>
       <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8" t="s">
-        <v>71</v>
+        <v>1380</v>
+      </c>
+      <c r="R8">
+        <v>980</v>
       </c>
       <c r="S8" t="s">
-        <v>72</v>
+        <v>64</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8" t="s">
+        <v>74</v>
+      </c>
+      <c r="V8" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -1231,117 +1312,135 @@
       <c r="Q9">
         <v>0</v>
       </c>
-      <c r="R9" t="s">
-        <v>71</v>
+      <c r="R9">
+        <v>0</v>
       </c>
       <c r="S9" t="s">
-        <v>72</v>
+        <v>64</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9" t="s">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P10">
         <v>2</v>
       </c>
       <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10" t="s">
+        <v>3160</v>
+      </c>
+      <c r="R10">
+        <v>2200</v>
+      </c>
+      <c r="S10" t="s">
+        <v>64</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10" t="s">
+        <v>82</v>
+      </c>
+      <c r="V10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" t="s">
         <v>79</v>
       </c>
-      <c r="S10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" t="s">
-        <v>76</v>
-      </c>
       <c r="I11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J11" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N11" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P11">
         <v>1</v>
@@ -1349,188 +1448,224 @@
       <c r="Q11">
         <v>0</v>
       </c>
-      <c r="R11" t="s">
-        <v>79</v>
+      <c r="R11">
+        <v>0</v>
       </c>
       <c r="S11" t="s">
+        <v>64</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11" t="s">
+        <v>82</v>
+      </c>
+      <c r="V11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" t="s">
+        <v>88</v>
+      </c>
+      <c r="J12" t="s">
+        <v>89</v>
+      </c>
+      <c r="K12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F12" t="s">
-        <v>82</v>
-      </c>
-      <c r="G12" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" t="s">
-        <v>85</v>
-      </c>
-      <c r="J12" t="s">
-        <v>86</v>
-      </c>
-      <c r="K12" t="s">
-        <v>29</v>
-      </c>
-      <c r="L12" t="s">
-        <v>30</v>
-      </c>
       <c r="M12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N12" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="O12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P12">
         <v>3</v>
       </c>
       <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12" t="s">
-        <v>87</v>
+        <v>1797</v>
+      </c>
+      <c r="R12">
+        <v>1560</v>
       </c>
       <c r="S12" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12" t="s">
+        <v>90</v>
+      </c>
+      <c r="V12" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I13" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="O13" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P13">
         <v>1</v>
       </c>
       <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13" t="s">
-        <v>96</v>
+        <v>1380</v>
+      </c>
+      <c r="R13">
+        <v>980</v>
       </c>
       <c r="S13" t="s">
-        <v>33</v>
+        <v>92</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13" t="s">
+        <v>99</v>
+      </c>
+      <c r="V13" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H14" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I14" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J14" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P14">
         <v>1</v>
       </c>
       <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14" t="s">
-        <v>33</v>
+        <v>1580</v>
+      </c>
+      <c r="R14">
+        <v>1100</v>
       </c>
       <c r="S14" t="s">
-        <v>33</v>
+        <v>23</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14" t="s">
+        <v>36</v>
+      </c>
+      <c r="V14" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/shipping/sample/momo訂單匯出範例.xlsx
+++ b/shipping/sample/momo訂單匯出範例.xlsx
@@ -837,7 +837,7 @@
         <v>599</v>
       </c>
       <c r="R2">
-        <v>520</v>
+        <v>175</v>
       </c>
       <c r="S2" t="s">
         <v>23</v>
@@ -905,7 +905,7 @@
         <v>1580</v>
       </c>
       <c r="R3">
-        <v>1100</v>
+        <v>110</v>
       </c>
       <c r="S3" t="s">
         <v>39</v>
@@ -973,7 +973,7 @@
         <v>1580</v>
       </c>
       <c r="R4">
-        <v>1100</v>
+        <v>110</v>
       </c>
       <c r="S4" t="s">
         <v>39</v>
@@ -1109,7 +1109,7 @@
         <v>1580</v>
       </c>
       <c r="R6">
-        <v>1100</v>
+        <v>110</v>
       </c>
       <c r="S6" t="s">
         <v>23</v>
@@ -1245,7 +1245,7 @@
         <v>1380</v>
       </c>
       <c r="R8">
-        <v>980</v>
+        <v>165</v>
       </c>
       <c r="S8" t="s">
         <v>64</v>
@@ -1381,7 +1381,7 @@
         <v>3160</v>
       </c>
       <c r="R10">
-        <v>2200</v>
+        <v>110</v>
       </c>
       <c r="S10" t="s">
         <v>64</v>
@@ -1517,7 +1517,7 @@
         <v>1797</v>
       </c>
       <c r="R12">
-        <v>1560</v>
+        <v>175</v>
       </c>
       <c r="S12" t="s">
         <v>28</v>
@@ -1585,7 +1585,7 @@
         <v>1380</v>
       </c>
       <c r="R13">
-        <v>980</v>
+        <v>165</v>
       </c>
       <c r="S13" t="s">
         <v>92</v>
@@ -1653,7 +1653,7 @@
         <v>1580</v>
       </c>
       <c r="R14">
-        <v>1100</v>
+        <v>110</v>
       </c>
       <c r="S14" t="s">
         <v>23</v>
